--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>81938419</v>
+        <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>73693</v>
+        <v>90855</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,34 +2936,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Alstjärnen, Ly lm</t>
+          <t>Källmyren NÖ, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628016.8257220474</v>
+        <v>627737</v>
       </c>
       <c r="R22" t="n">
-        <v>7171612.951055199</v>
+        <v>7171196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,22 +2990,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,22 +3010,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Helene Andersson, Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>81938491</v>
+        <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
+        <v>90833</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,34 +3042,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Alstjärnen, Ly lm</t>
+          <t>Källmyren NÖ, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628004.3497448133</v>
+        <v>627713</v>
       </c>
       <c r="R23" t="n">
-        <v>7171552.339480817</v>
+        <v>7171287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3102,22 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,22 +3116,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>81938510</v>
+        <v>81938419</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,21 +3148,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>627999.748120443</v>
+        <v>628016.8257220474</v>
       </c>
       <c r="R24" t="n">
-        <v>7171691.623518399</v>
+        <v>7171612.951055199</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,10 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81938509</v>
+        <v>81938491</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,21 +3260,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628017.7198219228</v>
+        <v>628004.3497448133</v>
       </c>
       <c r="R25" t="n">
-        <v>7171612.130540291</v>
+        <v>7171552.339480817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,6 +3353,230 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>81938510</v>
+      </c>
+      <c r="B26" t="n">
+        <v>77506</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Alstjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>627999.748120443</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7171691.623518399</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>81938509</v>
+      </c>
+      <c r="B27" t="n">
+        <v>77506</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Alstjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628017.7198219228</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7171612.130540291</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2923,7 +2923,7 @@
         <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90833</v>
+        <v>90936</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B22" t="n">
-        <v>90958</v>
+        <v>90940</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R22" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B23" t="n">
-        <v>90936</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R23" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Helene Andersson, Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R22" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R23" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R22" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sanna Strömberg , Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R23" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90940</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R22" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Helene Andersson, Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R23" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R22" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B23" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R23" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Helene Andersson, Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745316</v>
+        <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627713</v>
+        <v>627737</v>
       </c>
       <c r="R22" t="n">
-        <v>7171287</v>
+        <v>7171196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Helene Andersson, Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122745317</v>
+        <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627737</v>
+        <v>627713</v>
       </c>
       <c r="R23" t="n">
-        <v>7171196</v>
+        <v>7171287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2923,7 +2923,7 @@
         <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90948</v>
+        <v>90951</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 55889-2020 artfynd.xlsx
+++ b/artfynd/A 55889-2020 artfynd.xlsx
@@ -2923,7 +2923,7 @@
         <v>122745317</v>
       </c>
       <c r="B22" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>122745316</v>
       </c>
       <c r="B23" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
